--- a/T41_V012_Files/T41_V012_Assembled_PCBs/T41_RF_Board_DualClockDaughterBoard_V2_031426/T41_RF_Board_DualClock_Assy_BOM.xlsx
+++ b/T41_V012_Files/T41_V012_Assembled_PCBs/T41_RF_Board_DualClockDaughterBoard_V2_031426/T41_RF_Board_DualClock_Assy_BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\GitHub\T41\T41_V012_Files\T41_V012_BOMs\Source Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\GitHub\T41\T41_V012_Files\T41_V012_Assembled_PCBs\T41_RF_Board_DualClockDaughterBoard_V2_031426\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E73DEA-26BE-4A6C-8B52-FE77AABF91FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F824D9-7C7A-40C4-BFCE-A8A2216DB922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{E22704CE-DCA7-44D8-A808-A6A409B534BA}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
-  <si>
-    <t>Id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>Designator</t>
   </si>
@@ -47,12 +44,6 @@
     <t>Footprint</t>
   </si>
   <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Designation</t>
-  </si>
-  <si>
     <t>L1, L2, L3, L4</t>
   </si>
   <si>
@@ -68,70 +59,49 @@
     <t>QFN-20-1EP_4x4mm_P0.5mm_EP2.7x2.7mm</t>
   </si>
   <si>
-    <t>Si5351A-B-GM</t>
-  </si>
-  <si>
     <t>Oscillator_ECS_TXO53_S3</t>
   </si>
   <si>
-    <t>ECS-TX053-S3</t>
-  </si>
-  <si>
-    <t>C_0603_1608Metric</t>
-  </si>
-  <si>
-    <t>Manufacturer</t>
-  </si>
-  <si>
-    <t>Kemet</t>
-  </si>
-  <si>
-    <t>Manufacturer Number</t>
-  </si>
-  <si>
     <t>0.1uF 50V X7R 0603 SMD</t>
   </si>
   <si>
     <t>ECS-TXO53-S3-33-250-BN-TR</t>
   </si>
   <si>
-    <t>ECS</t>
-  </si>
-  <si>
-    <t>Laird Technologies</t>
-  </si>
-  <si>
-    <t>MI0603J601R-10</t>
-  </si>
-  <si>
     <t>Ferrite bead 600 mOhm 1A 0603 SMD</t>
   </si>
   <si>
-    <t>Skyworks</t>
-  </si>
-  <si>
     <t>Clock Generator Si5351A-B-GM</t>
   </si>
   <si>
     <t>R1, R2</t>
   </si>
   <si>
-    <t>R_0603_1608Metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Vishay</t>
-  </si>
-  <si>
     <t>2.2K Ohm 1% 1/8W</t>
   </si>
   <si>
-    <t>CRCW06032K20FKEC</t>
-  </si>
-  <si>
-    <t>C0603C104K5RACTU</t>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>JLCPCB Part #</t>
+  </si>
+  <si>
+    <t>C696359</t>
+  </si>
+  <si>
+    <t>C2441365</t>
+  </si>
+  <si>
+    <t>0603</t>
+  </si>
+  <si>
+    <t>C2105704</t>
+  </si>
+  <si>
+    <t>C19858592</t>
+  </si>
+  <si>
+    <t>C22413806</t>
   </si>
 </sst>
 </file>
@@ -181,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -190,6 +160,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -529,159 +502,97 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.7265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.453125" style="1" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="37.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="1"/>
-    <col min="5" max="5" width="32.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.90625" customWidth="1"/>
-    <col min="7" max="7" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>16</v>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="1">
-        <v>4</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="1">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/T41_V012_Files/T41_V012_Assembled_PCBs/T41_RF_Board_DualClockDaughterBoard_V2_031426/T41_RF_Board_DualClock_Assy_BOM.xlsx
+++ b/T41_V012_Files/T41_V012_Assembled_PCBs/T41_RF_Board_DualClockDaughterBoard_V2_031426/T41_RF_Board_DualClock_Assy_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\GitHub\T41\T41_V012_Files\T41_V012_Assembled_PCBs\T41_RF_Board_DualClockDaughterBoard_V2_031426\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F824D9-7C7A-40C4-BFCE-A8A2216DB922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A06E8EE-E4E6-4038-A223-5B53C3D2D836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{E22704CE-DCA7-44D8-A808-A6A409B534BA}"/>
   </bookViews>
@@ -89,19 +89,19 @@
     <t>C696359</t>
   </si>
   <si>
-    <t>C2441365</t>
-  </si>
-  <si>
     <t>0603</t>
   </si>
   <si>
     <t>C2105704</t>
   </si>
   <si>
-    <t>C19858592</t>
-  </si>
-  <si>
     <t>C22413806</t>
+  </si>
+  <si>
+    <t>C1002</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -533,7 +533,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -547,10 +547,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -561,10 +561,10 @@
         <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
         <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -578,7 +578,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -592,7 +592,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
